--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121645608</v>
+        <v>121645617</v>
       </c>
       <c r="B2" t="n">
-        <v>79234</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562985</v>
+        <v>563042</v>
       </c>
       <c r="R2" t="n">
-        <v>6354512</v>
+        <v>6354486</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645600</v>
+        <v>121645608</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>79234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563025</v>
+        <v>562985</v>
       </c>
       <c r="R3" t="n">
-        <v>6354440</v>
+        <v>6354512</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -912,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645634</v>
+        <v>121645600</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +927,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563042</v>
+        <v>563025</v>
       </c>
       <c r="R4" t="n">
-        <v>6354486</v>
+        <v>6354440</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,6 +1017,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121645617</v>
+        <v>121645634</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>57726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,37 +1048,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121645617</v>
+        <v>121645608</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>79234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563042</v>
+        <v>562985</v>
       </c>
       <c r="R2" t="n">
-        <v>6354486</v>
+        <v>6354512</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645608</v>
+        <v>121645600</v>
       </c>
       <c r="B3" t="n">
-        <v>79234</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +803,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562985</v>
+        <v>563025</v>
       </c>
       <c r="R3" t="n">
-        <v>6354512</v>
+        <v>6354440</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -915,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645600</v>
+        <v>121645617</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,35 +924,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563025</v>
+        <v>563042</v>
       </c>
       <c r="R4" t="n">
-        <v>6354440</v>
+        <v>6354486</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,7 +1018,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645600</v>
+        <v>121645617</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +803,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563025</v>
+        <v>563042</v>
       </c>
       <c r="R3" t="n">
-        <v>6354440</v>
+        <v>6354486</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,7 +897,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645617</v>
+        <v>121645600</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +927,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563042</v>
+        <v>563025</v>
       </c>
       <c r="R4" t="n">
-        <v>6354486</v>
+        <v>6354440</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,6 +1017,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645617</v>
+        <v>121645600</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563042</v>
+        <v>563025</v>
       </c>
       <c r="R3" t="n">
-        <v>6354486</v>
+        <v>6354440</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -897,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645600</v>
+        <v>121645617</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,35 +924,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563025</v>
+        <v>563042</v>
       </c>
       <c r="R4" t="n">
-        <v>6354440</v>
+        <v>6354486</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,7 +1018,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121645608</v>
+        <v>121645600</v>
       </c>
       <c r="B2" t="n">
-        <v>79234</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562985</v>
+        <v>563025</v>
       </c>
       <c r="R2" t="n">
-        <v>6354512</v>
+        <v>6354440</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645600</v>
+        <v>121645617</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563025</v>
+        <v>563042</v>
       </c>
       <c r="R3" t="n">
-        <v>6354440</v>
+        <v>6354486</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,7 +902,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645617</v>
+        <v>121645634</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,37 +932,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1036,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121645634</v>
+        <v>121645608</v>
       </c>
       <c r="B5" t="n">
-        <v>57726</v>
+        <v>79234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,39 +1056,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563042</v>
+        <v>562985</v>
       </c>
       <c r="R5" t="n">
-        <v>6354486</v>
+        <v>6354512</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1142,6 +1141,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121645600</v>
+        <v>121645634</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>57726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563025</v>
+        <v>563042</v>
       </c>
       <c r="R2" t="n">
-        <v>6354440</v>
+        <v>6354486</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -920,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645634</v>
+        <v>121645608</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>79234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,39 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563042</v>
+        <v>562985</v>
       </c>
       <c r="R4" t="n">
-        <v>6354486</v>
+        <v>6354512</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1026,6 +1020,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1044,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121645608</v>
+        <v>121645600</v>
       </c>
       <c r="B5" t="n">
-        <v>79234</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,30 +1051,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562985</v>
+        <v>563025</v>
       </c>
       <c r="R5" t="n">
-        <v>6354512</v>
+        <v>6354440</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121645634</v>
+        <v>121645608</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>79247</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563042</v>
+        <v>562985</v>
       </c>
       <c r="R2" t="n">
-        <v>6354486</v>
+        <v>6354512</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -802,7 +794,7 @@
         <v>121645617</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -923,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645608</v>
+        <v>121645600</v>
       </c>
       <c r="B4" t="n">
-        <v>79234</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +927,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562985</v>
+        <v>563025</v>
       </c>
       <c r="R4" t="n">
-        <v>6354512</v>
+        <v>6354440</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1039,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121645600</v>
+        <v>121645634</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>57734</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,35 +1048,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563025</v>
+        <v>563042</v>
       </c>
       <c r="R5" t="n">
-        <v>6354440</v>
+        <v>6354486</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,7 +1142,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121645608</v>
       </c>
       <c r="B2" t="n">
-        <v>79247</v>
+        <v>79249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645617</v>
+        <v>121645600</v>
       </c>
       <c r="B3" t="n">
-        <v>57518</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563042</v>
+        <v>563025</v>
       </c>
       <c r="R3" t="n">
-        <v>6354486</v>
+        <v>6354440</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -897,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645600</v>
+        <v>121645617</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>57518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,35 +924,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563025</v>
+        <v>563042</v>
       </c>
       <c r="R4" t="n">
-        <v>6354440</v>
+        <v>6354486</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,7 +1018,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54034-2024 artfynd.xlsx
+++ b/artfynd/A 54034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121645608</v>
+        <v>121645600</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562985</v>
+        <v>563025</v>
       </c>
       <c r="R2" t="n">
-        <v>6354512</v>
+        <v>6354440</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645600</v>
+        <v>121645617</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>57518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563025</v>
+        <v>563042</v>
       </c>
       <c r="R3" t="n">
-        <v>6354440</v>
+        <v>6354486</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,7 +902,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645617</v>
+        <v>121645634</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
+        <v>57734</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,37 +932,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1036,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121645634</v>
+        <v>121645608</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>79250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,39 +1056,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563042</v>
+        <v>562985</v>
       </c>
       <c r="R5" t="n">
-        <v>6354486</v>
+        <v>6354512</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1142,6 +1141,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
